--- a/artfynd/A 3940-2025 artfynd.xlsx
+++ b/artfynd/A 3940-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122837237</v>
+        <v>122837239</v>
       </c>
       <c r="B2" t="n">
-        <v>5173</v>
+        <v>100621</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570520</v>
+        <v>570424</v>
       </c>
       <c r="R2" t="n">
-        <v>6684965</v>
+        <v>6685090</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122837239</v>
+        <v>122837224</v>
       </c>
       <c r="B3" t="n">
-        <v>100613</v>
+        <v>4770</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,34 +793,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>100299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570424</v>
+        <v>570371</v>
       </c>
       <c r="R3" t="n">
-        <v>6685090</v>
+        <v>6685066</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122837224</v>
+        <v>122837237</v>
       </c>
       <c r="B4" t="n">
-        <v>4770</v>
+        <v>5173</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100299</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570371</v>
+        <v>570520</v>
       </c>
       <c r="R4" t="n">
-        <v>6685066</v>
+        <v>6684965</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122837235</v>
+        <v>122837241</v>
       </c>
       <c r="B5" t="n">
-        <v>92254</v>
+        <v>91605</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,25 +1003,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5964</v>
+        <v>898</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570427</v>
+        <v>570435</v>
       </c>
       <c r="R5" t="n">
-        <v>6685051</v>
+        <v>6685067</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1096,7 @@
         <v>122837238</v>
       </c>
       <c r="B6" t="n">
-        <v>100613</v>
+        <v>100621</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122837241</v>
+        <v>122837235</v>
       </c>
       <c r="B7" t="n">
-        <v>91601</v>
+        <v>92258</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,25 +1207,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>898</v>
+        <v>5964</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>570435</v>
+        <v>570427</v>
       </c>
       <c r="R7" t="n">
-        <v>6685067</v>
+        <v>6685051</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 3940-2025 artfynd.xlsx
+++ b/artfynd/A 3940-2025 artfynd.xlsx
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122837241</v>
+        <v>122837238</v>
       </c>
       <c r="B5" t="n">
-        <v>91605</v>
+        <v>100621</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,25 +1003,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>898</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570435</v>
+        <v>570416</v>
       </c>
       <c r="R5" t="n">
-        <v>6685067</v>
+        <v>6685092</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122837238</v>
+        <v>122837241</v>
       </c>
       <c r="B6" t="n">
-        <v>100621</v>
+        <v>91605</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,25 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>898</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570416</v>
+        <v>570435</v>
       </c>
       <c r="R6" t="n">
-        <v>6685092</v>
+        <v>6685067</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 3940-2025 artfynd.xlsx
+++ b/artfynd/A 3940-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122837239</v>
+        <v>122837224</v>
       </c>
       <c r="B2" t="n">
-        <v>100621</v>
+        <v>4770</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>100299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570424</v>
+        <v>570371</v>
       </c>
       <c r="R2" t="n">
-        <v>6685090</v>
+        <v>6685066</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122837224</v>
+        <v>122837239</v>
       </c>
       <c r="B3" t="n">
-        <v>4770</v>
+        <v>100621</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,39 +798,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100299</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570371</v>
+        <v>570424</v>
       </c>
       <c r="R3" t="n">
-        <v>6685066</v>
+        <v>6685090</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122837238</v>
+        <v>122837235</v>
       </c>
       <c r="B5" t="n">
-        <v>100621</v>
+        <v>92258</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570416</v>
+        <v>570427</v>
       </c>
       <c r="R5" t="n">
-        <v>6685092</v>
+        <v>6685051</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122837241</v>
+        <v>122837238</v>
       </c>
       <c r="B6" t="n">
-        <v>91605</v>
+        <v>100621</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,25 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>898</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570435</v>
+        <v>570416</v>
       </c>
       <c r="R6" t="n">
-        <v>6685067</v>
+        <v>6685092</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122837235</v>
+        <v>122837241</v>
       </c>
       <c r="B7" t="n">
-        <v>92258</v>
+        <v>91605</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,25 +1207,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5964</v>
+        <v>898</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>570427</v>
+        <v>570435</v>
       </c>
       <c r="R7" t="n">
-        <v>6685051</v>
+        <v>6685067</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 3940-2025 artfynd.xlsx
+++ b/artfynd/A 3940-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>122837239</v>
       </c>
       <c r="B3" t="n">
-        <v>100621</v>
+        <v>100623</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122837237</v>
+        <v>122837235</v>
       </c>
       <c r="B4" t="n">
-        <v>5173</v>
+        <v>92258</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,39 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>5964</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570520</v>
+        <v>570427</v>
       </c>
       <c r="R4" t="n">
-        <v>6684965</v>
+        <v>6685051</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122837235</v>
+        <v>122837238</v>
       </c>
       <c r="B5" t="n">
-        <v>92258</v>
+        <v>100623</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570427</v>
+        <v>570416</v>
       </c>
       <c r="R5" t="n">
-        <v>6685051</v>
+        <v>6685092</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122837238</v>
+        <v>122837237</v>
       </c>
       <c r="B6" t="n">
-        <v>100621</v>
+        <v>5173</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,34 +1104,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570416</v>
+        <v>570520</v>
       </c>
       <c r="R6" t="n">
-        <v>6685092</v>
+        <v>6684965</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 3940-2025 artfynd.xlsx
+++ b/artfynd/A 3940-2025 artfynd.xlsx
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122837238</v>
+        <v>122837237</v>
       </c>
       <c r="B5" t="n">
-        <v>100623</v>
+        <v>5173</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,34 +1002,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570416</v>
+        <v>570520</v>
       </c>
       <c r="R5" t="n">
-        <v>6685092</v>
+        <v>6684965</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122837237</v>
+        <v>122837238</v>
       </c>
       <c r="B6" t="n">
-        <v>5173</v>
+        <v>100623</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,39 +1109,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570520</v>
+        <v>570416</v>
       </c>
       <c r="R6" t="n">
-        <v>6684965</v>
+        <v>6685092</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 3940-2025 artfynd.xlsx
+++ b/artfynd/A 3940-2025 artfynd.xlsx
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122837237</v>
+        <v>122837238</v>
       </c>
       <c r="B5" t="n">
-        <v>5173</v>
+        <v>100623</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,39 +1002,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570520</v>
+        <v>570416</v>
       </c>
       <c r="R5" t="n">
-        <v>6684965</v>
+        <v>6685092</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122837238</v>
+        <v>122837237</v>
       </c>
       <c r="B6" t="n">
-        <v>100623</v>
+        <v>5173</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,34 +1104,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570416</v>
+        <v>570520</v>
       </c>
       <c r="R6" t="n">
-        <v>6685092</v>
+        <v>6684965</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 3940-2025 artfynd.xlsx
+++ b/artfynd/A 3940-2025 artfynd.xlsx
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122837239</v>
+        <v>122837238</v>
       </c>
       <c r="B3" t="n">
         <v>100623</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570424</v>
+        <v>570416</v>
       </c>
       <c r="R3" t="n">
-        <v>6685090</v>
+        <v>6685092</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122837235</v>
+        <v>122837241</v>
       </c>
       <c r="B4" t="n">
-        <v>92258</v>
+        <v>91605</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5964</v>
+        <v>898</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570427</v>
+        <v>570435</v>
       </c>
       <c r="R4" t="n">
-        <v>6685051</v>
+        <v>6685067</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122837238</v>
+        <v>122837239</v>
       </c>
       <c r="B5" t="n">
         <v>100623</v>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570416</v>
+        <v>570424</v>
       </c>
       <c r="R5" t="n">
-        <v>6685092</v>
+        <v>6685090</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122837237</v>
+        <v>122837235</v>
       </c>
       <c r="B6" t="n">
-        <v>5173</v>
+        <v>92258</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,39 +1104,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>5964</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570520</v>
+        <v>570427</v>
       </c>
       <c r="R6" t="n">
-        <v>6684965</v>
+        <v>6685051</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122837241</v>
+        <v>122837237</v>
       </c>
       <c r="B7" t="n">
-        <v>91605</v>
+        <v>5173</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,38 +1202,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>898</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>570435</v>
+        <v>570520</v>
       </c>
       <c r="R7" t="n">
-        <v>6685067</v>
+        <v>6684965</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 3940-2025 artfynd.xlsx
+++ b/artfynd/A 3940-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122837224</v>
+        <v>122837239</v>
       </c>
       <c r="B2" t="n">
-        <v>4770</v>
+        <v>100631</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100299</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570371</v>
+        <v>570424</v>
       </c>
       <c r="R2" t="n">
-        <v>6685066</v>
+        <v>6685090</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122837238</v>
+        <v>122837224</v>
       </c>
       <c r="B3" t="n">
-        <v>100623</v>
+        <v>4770</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,34 +793,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>100299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570416</v>
+        <v>570371</v>
       </c>
       <c r="R3" t="n">
-        <v>6685092</v>
+        <v>6685066</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122837241</v>
+        <v>122837238</v>
       </c>
       <c r="B4" t="n">
-        <v>91605</v>
+        <v>100631</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>898</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570435</v>
+        <v>570416</v>
       </c>
       <c r="R4" t="n">
-        <v>6685067</v>
+        <v>6685092</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122837239</v>
+        <v>122837237</v>
       </c>
       <c r="B5" t="n">
-        <v>100623</v>
+        <v>5173</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,34 +1002,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570424</v>
+        <v>570520</v>
       </c>
       <c r="R5" t="n">
-        <v>6685090</v>
+        <v>6684965</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122837235</v>
+        <v>122837241</v>
       </c>
       <c r="B6" t="n">
-        <v>92258</v>
+        <v>91613</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,25 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5964</v>
+        <v>898</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570427</v>
+        <v>570435</v>
       </c>
       <c r="R6" t="n">
-        <v>6685051</v>
+        <v>6685067</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122837237</v>
+        <v>122837235</v>
       </c>
       <c r="B7" t="n">
-        <v>5173</v>
+        <v>92266</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,39 +1211,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>5964</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>570520</v>
+        <v>570427</v>
       </c>
       <c r="R7" t="n">
-        <v>6684965</v>
+        <v>6685051</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 3940-2025 artfynd.xlsx
+++ b/artfynd/A 3940-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122837239</v>
+        <v>122837235</v>
       </c>
       <c r="B2" t="n">
-        <v>100631</v>
+        <v>92266</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570424</v>
+        <v>570427</v>
       </c>
       <c r="R2" t="n">
-        <v>6685090</v>
+        <v>6685051</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122837224</v>
+        <v>122837238</v>
       </c>
       <c r="B3" t="n">
-        <v>4770</v>
+        <v>100631</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,39 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100299</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570371</v>
+        <v>570416</v>
       </c>
       <c r="R3" t="n">
-        <v>6685066</v>
+        <v>6685092</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122837238</v>
+        <v>122837241</v>
       </c>
       <c r="B4" t="n">
-        <v>100631</v>
+        <v>91613</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>898</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570416</v>
+        <v>570435</v>
       </c>
       <c r="R4" t="n">
-        <v>6685092</v>
+        <v>6685067</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122837237</v>
+        <v>122837239</v>
       </c>
       <c r="B5" t="n">
-        <v>5173</v>
+        <v>100631</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,39 +997,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570520</v>
+        <v>570424</v>
       </c>
       <c r="R5" t="n">
-        <v>6684965</v>
+        <v>6685090</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122837241</v>
+        <v>122837224</v>
       </c>
       <c r="B6" t="n">
-        <v>91613</v>
+        <v>4770</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,38 +1095,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>898</v>
+        <v>100299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570435</v>
+        <v>570371</v>
       </c>
       <c r="R6" t="n">
-        <v>6685067</v>
+        <v>6685066</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122837235</v>
+        <v>122837237</v>
       </c>
       <c r="B7" t="n">
-        <v>92266</v>
+        <v>5173</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,34 +1206,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5964</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>570427</v>
+        <v>570520</v>
       </c>
       <c r="R7" t="n">
-        <v>6685051</v>
+        <v>6684965</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 3940-2025 artfynd.xlsx
+++ b/artfynd/A 3940-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122837235</v>
+        <v>122837241</v>
       </c>
       <c r="B2" t="n">
-        <v>92266</v>
+        <v>91613</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5964</v>
+        <v>898</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570427</v>
+        <v>570435</v>
       </c>
       <c r="R2" t="n">
-        <v>6685051</v>
+        <v>6685067</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122837238</v>
+        <v>122837235</v>
       </c>
       <c r="B3" t="n">
-        <v>100631</v>
+        <v>92266</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570416</v>
+        <v>570427</v>
       </c>
       <c r="R3" t="n">
-        <v>6685092</v>
+        <v>6685051</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122837241</v>
+        <v>122837224</v>
       </c>
       <c r="B4" t="n">
-        <v>91613</v>
+        <v>4770</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,38 +891,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>898</v>
+        <v>100299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570435</v>
+        <v>570371</v>
       </c>
       <c r="R4" t="n">
-        <v>6685067</v>
+        <v>6685066</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122837239</v>
+        <v>122837238</v>
       </c>
       <c r="B5" t="n">
         <v>100631</v>
@@ -1021,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570424</v>
+        <v>570416</v>
       </c>
       <c r="R5" t="n">
-        <v>6685090</v>
+        <v>6685092</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122837224</v>
+        <v>122837239</v>
       </c>
       <c r="B6" t="n">
-        <v>4770</v>
+        <v>100631</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,39 +1104,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100299</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570371</v>
+        <v>570424</v>
       </c>
       <c r="R6" t="n">
-        <v>6685066</v>
+        <v>6685090</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 3940-2025 artfynd.xlsx
+++ b/artfynd/A 3940-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122837241</v>
+        <v>122837237</v>
       </c>
       <c r="B2" t="n">
-        <v>91613</v>
+        <v>5173</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>898</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570435</v>
+        <v>570520</v>
       </c>
       <c r="R2" t="n">
-        <v>6685067</v>
+        <v>6684965</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122837235</v>
+        <v>122837224</v>
       </c>
       <c r="B3" t="n">
-        <v>92266</v>
+        <v>4770</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +798,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5964</v>
+        <v>100299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570427</v>
+        <v>570371</v>
       </c>
       <c r="R3" t="n">
-        <v>6685051</v>
+        <v>6685066</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122837224</v>
+        <v>122837238</v>
       </c>
       <c r="B4" t="n">
-        <v>4770</v>
+        <v>100631</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,39 +905,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100299</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570371</v>
+        <v>570416</v>
       </c>
       <c r="R4" t="n">
-        <v>6685066</v>
+        <v>6685092</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122837238</v>
+        <v>122837235</v>
       </c>
       <c r="B5" t="n">
-        <v>100631</v>
+        <v>92266</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570416</v>
+        <v>570427</v>
       </c>
       <c r="R5" t="n">
-        <v>6685092</v>
+        <v>6685051</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1190,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122837237</v>
+        <v>122837241</v>
       </c>
       <c r="B7" t="n">
-        <v>5173</v>
+        <v>91613</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,43 +1207,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>898</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>570520</v>
+        <v>570435</v>
       </c>
       <c r="R7" t="n">
-        <v>6684965</v>
+        <v>6685067</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 3940-2025 artfynd.xlsx
+++ b/artfynd/A 3940-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122837237</v>
+        <v>122837239</v>
       </c>
       <c r="B2" t="n">
-        <v>5173</v>
+        <v>100634</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570520</v>
+        <v>570424</v>
       </c>
       <c r="R2" t="n">
-        <v>6684965</v>
+        <v>6685090</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122837224</v>
+        <v>122837235</v>
       </c>
       <c r="B3" t="n">
-        <v>4770</v>
+        <v>92269</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,39 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100299</v>
+        <v>5964</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570371</v>
+        <v>570427</v>
       </c>
       <c r="R3" t="n">
-        <v>6685066</v>
+        <v>6685051</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122837238</v>
+        <v>122837224</v>
       </c>
       <c r="B4" t="n">
-        <v>100631</v>
+        <v>4770</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,34 +895,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>100299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570416</v>
+        <v>570371</v>
       </c>
       <c r="R4" t="n">
-        <v>6685092</v>
+        <v>6685066</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122837235</v>
+        <v>122837238</v>
       </c>
       <c r="B5" t="n">
-        <v>92266</v>
+        <v>100634</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570427</v>
+        <v>570416</v>
       </c>
       <c r="R5" t="n">
-        <v>6685051</v>
+        <v>6685092</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122837239</v>
+        <v>122837241</v>
       </c>
       <c r="B6" t="n">
-        <v>100631</v>
+        <v>91616</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,25 +1100,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>898</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570424</v>
+        <v>570435</v>
       </c>
       <c r="R6" t="n">
-        <v>6685090</v>
+        <v>6685067</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122837241</v>
+        <v>122837237</v>
       </c>
       <c r="B7" t="n">
-        <v>91613</v>
+        <v>5173</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,38 +1202,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>898</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>570435</v>
+        <v>570520</v>
       </c>
       <c r="R7" t="n">
-        <v>6685067</v>
+        <v>6684965</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 3940-2025 artfynd.xlsx
+++ b/artfynd/A 3940-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122837239</v>
+        <v>122837241</v>
       </c>
       <c r="B2" t="n">
-        <v>100634</v>
+        <v>91618</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>898</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570424</v>
+        <v>570435</v>
       </c>
       <c r="R2" t="n">
-        <v>6685090</v>
+        <v>6685067</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122837235</v>
+        <v>122837238</v>
       </c>
       <c r="B3" t="n">
-        <v>92269</v>
+        <v>100636</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570427</v>
+        <v>570416</v>
       </c>
       <c r="R3" t="n">
-        <v>6685051</v>
+        <v>6685092</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122837224</v>
+        <v>122837237</v>
       </c>
       <c r="B4" t="n">
-        <v>4770</v>
+        <v>5173</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100299</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570371</v>
+        <v>570520</v>
       </c>
       <c r="R4" t="n">
-        <v>6685066</v>
+        <v>6684965</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122837238</v>
+        <v>122837224</v>
       </c>
       <c r="B5" t="n">
-        <v>100634</v>
+        <v>4770</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,34 +1002,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>100299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570416</v>
+        <v>570371</v>
       </c>
       <c r="R5" t="n">
-        <v>6685092</v>
+        <v>6685066</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122837241</v>
+        <v>122837239</v>
       </c>
       <c r="B6" t="n">
-        <v>91616</v>
+        <v>100636</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,25 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>898</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570435</v>
+        <v>570424</v>
       </c>
       <c r="R6" t="n">
-        <v>6685067</v>
+        <v>6685090</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122837237</v>
+        <v>122837235</v>
       </c>
       <c r="B7" t="n">
-        <v>5173</v>
+        <v>92271</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,39 +1211,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>5964</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>570520</v>
+        <v>570427</v>
       </c>
       <c r="R7" t="n">
-        <v>6684965</v>
+        <v>6685051</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 3940-2025 artfynd.xlsx
+++ b/artfynd/A 3940-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122837241</v>
       </c>
       <c r="B2" t="n">
-        <v>91618</v>
+        <v>91624</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122837238</v>
+        <v>122837237</v>
       </c>
       <c r="B3" t="n">
-        <v>100636</v>
+        <v>5173</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +793,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570416</v>
+        <v>570520</v>
       </c>
       <c r="R3" t="n">
-        <v>6685092</v>
+        <v>6684965</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122837237</v>
+        <v>122837239</v>
       </c>
       <c r="B4" t="n">
-        <v>5173</v>
+        <v>100642</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,39 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570520</v>
+        <v>570424</v>
       </c>
       <c r="R4" t="n">
-        <v>6684965</v>
+        <v>6685090</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122837224</v>
+        <v>122837238</v>
       </c>
       <c r="B5" t="n">
-        <v>4770</v>
+        <v>100642</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,39 +1002,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100299</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570371</v>
+        <v>570416</v>
       </c>
       <c r="R5" t="n">
-        <v>6685066</v>
+        <v>6685092</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122837239</v>
+        <v>122837224</v>
       </c>
       <c r="B6" t="n">
-        <v>100636</v>
+        <v>4770</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,34 +1104,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>100299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570424</v>
+        <v>570371</v>
       </c>
       <c r="R6" t="n">
-        <v>6685090</v>
+        <v>6685066</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1198,7 @@
         <v>122837235</v>
       </c>
       <c r="B7" t="n">
-        <v>92271</v>
+        <v>92277</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
